--- a/tiflow-xborder/develop/2.0.0-ballot.2/ValueSet-GEM-ERPEU-VS-Consent-PolicyRule.xlsx
+++ b/tiflow-xborder/develop/2.0.0-ballot.2/ValueSet-GEM-ERPEU-VS-Consent-PolicyRule.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/erp-eu/ValueSet/GEM_ERPEU_VS_Consent_PolicyRule</t>
+    <t>https://gematik.de/fhir/tiflow-xborder/ValueSet/GEM-ERPEU-VS-Consent-PolicyRule</t>
   </si>
   <si>
     <t>Version</t>
